--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_advice/lang_advice__ui__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_advice/lang_advice__ui__part_0001.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Resonance Energy</t>
+          <t>Năng lượng Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Scanner</t>
+          <t>Máy Quét</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Điểm Treo Móc</t>
+          <t>Điểm Neo Bám</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Counter-Attack</t>
+          <t>Phản Công</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Material</t>
+          <t>Vật liệu</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Dân Lưu Đày</t>
+          <t>Dân Lưu Đày Thường</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Class Calamity</t>
+          <t>Hạng Thảm Họa</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Loại tinh nhuệ</t>
+          <t>Hạng Cao Cấp</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Glider</t>
+          <t>Dù Lượn Tay</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Cooking</t>
+          <t>Nấu ăn</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Squeak Express</t>
+          <t>Tàu Squeak Tốc Hành</t>
         </is>
       </c>
     </row>
